--- a/branches/feature/fix-katheter-pce/StructureDefinition-mii-pr-kardio-observation-rauchen.xlsx
+++ b/branches/feature/fix-katheter-pce/StructureDefinition-mii-pr-kardio-observation-rauchen.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T14:24:17+00:00</t>
+    <t>2026-10-02T12:47:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feature/fix-katheter-pce/StructureDefinition-mii-pr-kardio-observation-rauchen.xlsx
+++ b/branches/feature/fix-katheter-pce/StructureDefinition-mii-pr-kardio-observation-rauchen.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-02T12:47:32+00:00</t>
+    <t>2026-10-02T14:42:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
